--- a/data/mistral_traduzioni_con_score.xlsx
+++ b/data/mistral_traduzioni_con_score.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,36 @@
           <t>Feedback</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>BERTScore</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>COMET-22</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>BLEURT</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BLEU</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>chrF++</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TER (inv)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +559,24 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "era ben condotta" for "ben fatta l'opera" shows a good adaptation of archaic language into contemporary Italian. However, the phrase "di grande forza" could have been more elegantly expressed as "di grande abilità" to better match the original's tone. The translation also loses some of the poetic nuance present in the original, particularly in the description of Aiace. While the overall meaning is preserved, the slight awkwardness in certain phrases indicates that the translation is not fully polished. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>0.8538</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7937</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6002</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5762</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4737</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -577,6 +625,18 @@
           <t>The translation captures the essence of the original text and conveys the main message about revenge and justice. However, it uses "prescrive" instead of "dice," which slightly alters the meaning from "says" to "prescribes." Additionally, the phrase "non perdona nessun cavaliere" is a bit too literal compared to the original "a neuno cavaliere perdoni," making it sound somewhat mechanical. While the translation is comprehensible and maintains the basic structure, it lacks the poetic nuance of the original, particularly in the final part where "pecchi" is replaced with "sbagli." The modernization of the text is adequate but could benefit from more idiomatic expressions to better reflect the medieval context. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>0.8388</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6234</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -625,6 +685,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "non fu dotato di minore forza d’animo" effectively conveys the meaning of "ornato" and "forza d' animo," though it could have been more elegant. The phrase "cavaliere romano" is appropriately preserved, but the construction "non fu dotato" feels slightly mechanical compared to the original's more poetic expression. While the translation is comprehensible and conveys the intended message, it lacks the nuanced elegance of a higher-scoring translation. The modernization of the archaic terms is adequate but not fully polished.</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -675,6 +747,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "volontà comune" instead of a more literal translation of "piace a tutti" shows a good adaptation to contemporary language. However, the phrase "circostanze richiedono" could have been expressed more elegantly, and the term "guida" might not fully capture the connotation of "cavaliere" in this context. The translation is comprehensible and conveys the main message, but it lacks some of the stylistic finesse that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>0.7887</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7604</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -725,6 +809,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax, though it could have been more elegant in expressing the concept of "appostatamente". The use of "parlare in modo appropriato" for "dicere appostatamente" is functional but slightly mechanical, showing a slight loss of the original's subtlety. The phrase "il suo fine" is a good adaptation of "fine è", but the overall flow could be smoother. While the translation is comprehensible and conveys the main message, it lacks the poetic nuance of the original, making it read more like a standard translation rather than a refined rendering of archaic language.</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>0.8203</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8577</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8317</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -765,6 +861,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian language structure. The use of "scrosci di pioggia" instead of "ventipiovoli" shows a good attempt at modernizing the archaic term, though it could have been more precise. The phrase "stia precipitando" is a good adaptation of "cadesse," but it's slightly less poetic than the original. The translation is comprehensible and conveys the intended meaning, but it lacks some of the stylistic elegance of the original. While it maintains the basic meaning and readability, it doesn't fully capture the poetic nature of the original text. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>0.8935</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.8371</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.7029</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -809,6 +917,18 @@
           <t>The translation captures the essence of the original text and maintains its meaning, though it could have been more elegant in certain phrases. The use of "coloro che" instead of "quegli che" is a good adaptation of the archaic term, but the phrase "digrignano i denti" feels slightly mechanical compared to the original "stridono colli denti." The syntax is modern and comprehensible, but there's room for improvement in the flow and naturalness of the expression. While the translation is accurate, it doesn't fully capture the poetic quality of the original text, particularly in the final part where the metaphorical language could have been rendered more smoothly. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>0.8577</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7053</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.6963</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -853,6 +973,18 @@
           <t>The translation captures the main idea of the original text but exhibits some mechanical qualities. While it conveys the basic meaning of the archaic Italian text, the phrasing "causò la vendita" feels slightly literal and could have been expressed more naturally. The term "beni" for "morti" is a somewhat awkward choice, though it's understandable. The translation maintains the core message about the king's fraud and the relationship between the dead and living, but lacks the poetic flair of the original. The syntax follows modern Italian conventions but doesn't fully capture the historical tone of the source text. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>0.8294</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6176</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -897,6 +1029,18 @@
           <t>The translation captures the essence of the original text but shows some mechanical traits in its construction. While it successfully conveys the main message about the father's son being tormented due to his impiety, the use of "colui che" instead of "colui, che" slightly alters the archaic tone. The phrase "per le sue grandi colpe" is a somewhat literal translation of "gran reità," which could have been rendered more naturally as "grandi imprese." Additionally, the word "rispettato" is a good choice but feels slightly out of place in this context. The translation maintains readability and preserves the core meaning, though it lacks the full richness of the original medieval style.</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8545</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.7497</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -947,6 +1091,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The phrase "spesso" is appropriately used instead of "spessamente," which makes it more accessible to contemporary readers. However, the use of "rimanendo" instead of "stare" introduces a slight awkwardness in the flow, though it's still comprehensible. The translation successfully conveys the philosophical concept of truth and falsehood, but the construction "nella menzogna" could have been more elegantly expressed. While the translation is functional and understandable, it lacks the smoothness and naturalness that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>0.8544</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8675</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.8141</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -991,6 +1147,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The phrase "che faceva parte" effectively conveys the meaning of "ch'era de' dieci compagni," though it could have been more elegant. The use of "con attenzione e prudenza" is a good adaptation of "studiosamente," but it slightly shifts the original nuance. The translation is comprehensible and maintains the formal tone of the original, yet it lacks the full richness of the archaic language. While it's a solid translation, it doesn't fully capture the historical flavor of the original text, making it feel somewhat mechanical in places.</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8632</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7554999999999999</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1035,6 +1203,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. However, it slightly deviates from the expected result by adding "che" after "io," which makes the sentence structure less natural than the reference translation. While the core meaning is preserved, the addition of "che" creates a slight awkwardness in the flow of the text. The translation is comprehensible and conveys the intended message, but the use of "esser state" instead of "fatte" introduces a minor stylistic inconsistency. Despite these small issues, the translation remains readable and maintains the basic meaning of the original text.</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>0.8676</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1083,6 +1263,18 @@
           <t>The translation is flawless, capturing the essence of the original text while maintaining a modern Italian syntax. The archaic term 'Corbio' is preserved with precision, and the phrase 'menò sua vita' is elegantly transformed into 'condusse una vita', which is both accurate and idiomatic. The use of 'più bassa e più viziosa' perfectly conveys the original's negative connotations without losing any nuance. The sentence structure flows naturally, demonstrating a deep understanding of both languages and their respective conventions."</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>0.9562</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.9649</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.9443</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1133,6 +1325,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "merzé" is appropriately contextualized with a parenthetical explanation, though it could have been more elegantly integrated into the sentence structure. The phrase "nel suo discorso" is a good adaptation of "in suo dire," but the overall flow could be smoother. While the translation is comprehensible and conveys the main message, it occasionally leans towards a literal interpretation, particularly in the rendering of "altressì." The text achieves readability but lacks the nuanced expression that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>0.8529</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7169</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.6448</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1179,6 +1383,18 @@
           <t>The translation exhibits several issues that make it difficult to understand the original text. The phrase "misai in disordine i capelli" is a literal translation of "scapigliai," which is incorrect in this context. The word "capelli" is used instead of "donna," which changes the meaning completely. Additionally, the use of "Oh, quanti giorni" instead of "Ohimè, quante giornate" fails to capture the archaic tone of the original text. The syntax is awkward and lacks the flow of the original, making it read like a machine translation. The translation also omits the reference to chapter 347, which was present in the original text. The overall result is a text that is not only inaccurate but also fails to convey the emotional intensity of the original.</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>0.7825</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6399</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1225,6 +1441,18 @@
           <t>The translation captures the essence of the original text and maintains its meaning, though it could have been more elegant in its phrasing. The use of "erano" instead of "era" slightly shifts the meaning from singular to plural, which is not entirely accurate to the original text. The syntax is modern and comprehensible, but the expression "perché era" feels somewhat mechanical compared to the more natural "che era". While the translation is functional and conveys the message, it lacks the refinement and nuance that would elevate it to a higher score. The text is readable and understandable, but it doesn't fully capture the poetic nature of the original. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>0.8384</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8546</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7427</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1269,6 +1497,18 @@
           <t>The translation captures the essence of the original text and maintains its meaning, though it shows some mechanical traits. The use of "non conoscevano" instead of "non sapevano" slightly alters the tone, making it less archaic than the source text. The phrase "perché la donna non aveva ancora nominato i nomi" is a good adaptation of the original, but it could have been more idiomatic. The syntax is modern and comprehensible, but the translation lacks the full richness of the original's linguistic style. While the translation is serviceable and conveys the message, it doesn't fully capture the historical nuance of the medieval language. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>0.9348</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.9411</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8792</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1313,6 +1553,18 @@
           <t>The translation captures the essence of the original text and maintains its archaic tone, though it occasionally uses slightly mechanical language. The phrase "al mio posto" is a good adaptation of the original "in mio luogo," but the use of quotation marks around "ospite troiano" feels somewhat forced and could have been expressed more naturally. The translation successfully conveys the main message but lacks some of the stylistic finesse that would elevate it to a higher score. While it's clear and comprehensible, it doesn't fully capture the poetic nature of the original text. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>0.8788</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7844</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7539</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1361,6 +1613,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "fu scoperta" instead of "fu ripressa" shows a good attempt at adapting archaic language to contemporary Italian, though it could have been more precise. The phrase "in una simile menzogna" is a good adaptation of "in simile bugìa," but the choice of "menzogna" over "bugia" slightly diminishes the historical flavor. The translation is generally fluent and comprehensible, but there's room for improvement in preserving the medieval tone. While it successfully conveys the meaning, it doesn't fully capture the stylistic nuances of the original text.</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>0.8546</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.6348</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1405,6 +1669,18 @@
           <t>The translation captures the essence of the original text and conveys the main ideas accurately. The use of "si lamentavano" instead of "lamentavansi" is a good adaptation to modern Italian, while "piangevano" for "ripiagnevano" is a suitable choice. However, the phrase "sfortunata bellezza" could have been more elegantly expressed as "sventurata bellezza," which would have better preserved the archaic tone. The translation is comprehensible and maintains the emotional weight of the original, though it lacks some of the stylistic finesse that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>0.9273</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8915999999999999</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8396</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1453,6 +1729,18 @@
           <t>The translation captures the essence of the original text and conveys the main ideas accurately, but there are some noticeable issues. The phrase "certamente ebbi sempre il coraggio" is a bit too literal and lacks the nuance of "ardire," which could have been better expressed as "coraggio di parlare." Additionally, "mi dolevo" is a somewhat awkward choice for "dolfi," as it doesn't fully capture the emotional depth of the original. While the translation is comprehensible and maintains the basic meaning, it occasionally falls into slightly mechanical phrasing, particularly in the second sentence where the structure feels less natural than ideal. The translation successfully renders the core message but misses some of the stylistic finesse of the original. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>0.8401</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1497,6 +1785,18 @@
           <t>The translation captures the basic meaning of the original text but shows some mechanical traits in its construction. The use of "talvolta" instead of "talora" is a good adaptation, but the phrase "a causa della grande prudenza" feels slightly literal and could have been expressed more naturally. The term "qualcun altro" for "altrui" is a good choice, though it slightly changes the original meaning. The syntax follows the original too closely, making it read somewhat like a machine translation. While the translation is comprehensible and conveys the main idea, it lacks the stylistic refinement expected of a higher-quality translation. The handling of archaic terms is adequate but not optimal, and the overall flow could be smoother.</t>
         </is>
       </c>
+      <c r="K23" t="n">
+        <v>0.7472</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5164</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1545,6 +1845,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "condusse con sé" instead of "portò con sé" shows a slight preference for a more formal expression, which is appropriate for the context. However, the phrase "della legione" could have been better expressed as "della legione romana" to provide additional clarity about the subject. The translation is generally fluent and comprehensible, though it occasionally leans towards a slightly mechanical rendering of the original. While it successfully conveys the main idea, it lacks some of the stylistic finesse that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K24" t="n">
+        <v>0.9366</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.8853</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.9067</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1589,6 +1901,18 @@
           <t>The translation captures the essence of the original text and maintains its basic meaning, but there are noticeable issues with the archaic language adaptation. The term "cognoscere" is replaced with the more modern "riconoscere," which is appropriate, but the use of "colei" instead of "quella" shows a slight over-correction towards modernity. The phrase "diede coraggio" is a good modern equivalent for "diede ardire," though it loses some of the original's poetic nuance. The syntax is generally correct, but the translation occasionally feels slightly mechanical, particularly in the construction of the second sentence. While comprehensible, the translation doesn't fully capture the stylistic richness of the original medieval text.</t>
         </is>
       </c>
+      <c r="K25" t="n">
+        <v>0.8579</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.8257</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6972</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1633,6 +1957,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "passarono" instead of "passavano" reflects a good understanding of the past tense, though it could have been more precise. The phrase "non avesse avuto coraggio in ciò" is a good adaptation of "non avesse ardire de questo," but it slightly loses the emotional weight of the original. The translation is comprehensible and conveys the main ideas, but there's room for improvement in capturing the full nuance of the medieval context. While the text flows naturally, it occasionally uses slightly mechanical constructions, such as the transition between sentences. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K26" t="n">
+        <v>0.8104</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.6623</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1677,6 +2013,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "Per questo" instead of "Per questo motivo" shows a slight preference for simplicity over formality, which is acceptable in this context. However, the phrase "come dolente" could have been more elegantly expressed as "come sofferente," which would have better preserved the archaic tone of the original. The translation is comprehensible and conveys the main idea, but it lacks the nuanced expression of the original's emotional depth. While the translation is serviceable, it doesn't fully capture the poetic nature of the source text. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K27" t="n">
+        <v>0.8686</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.7105</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1721,6 +2069,18 @@
           <t>The translation captures the essence of the original text and maintains its formal tone, though it occasionally uses slightly mechanical constructions such as "con maggior sicurezza" instead of a more idiomatic expression. While the core meaning is preserved, there's room for improvement in terms of naturalness and flow, particularly in the transition between sentences. The archaic elements have been appropriately modernized, but some phrases could benefit from a more nuanced rendering to better reflect the historical context. The translation is comprehensible and conveys the message effectively, though it lacks the polish of a truly excellent translation.</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>0.9008</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.8379</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1765,6 +2125,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "poiché" instead of "con ciò" represents a good adaptation of the archaic expression into contemporary language. However, the phrase "abbia scritto" could have been more elegantly expressed as "scrisse" to better reflect the original's style. Additionally, the term "essi" in the reference translation was replaced with "di esso," which slightly alters the meaning. While the translation is generally accurate and comprehensible, it lacks the full richness of the original's archaic tone, making it feel somewhat mechanical in places.</t>
         </is>
       </c>
+      <c r="K29" t="n">
+        <v>0.9013</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8006</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1809,6 +2181,18 @@
           <t>The translation captures the essence of the original text and maintains its philosophical tone, though it occasionally uses slightly mechanical constructions such as "se non fosse così frequentemente usata" instead of a more idiomatic expression. The use of "dato che" for "posto che" is a good choice, but the overall structure feels somewhat rigid and lacks the natural flow of a native speaker's language. While the translation conveys the main ideas accurately, it doesn't fully capture the poetic nature of the original text, particularly in the final part where "lo spirito umano si riferisce a quello divino" could have been expressed more elegantly. The translation is comprehensible and retains the core meaning, but there's room for improvement in terms of style and expression.</t>
         </is>
       </c>
+      <c r="K30" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.7614</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.6004</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1859,6 +2243,18 @@
           <t>The translation captures the essence of the original text and maintains its basic meaning, but there are noticeable issues with word choice and phrasing. For instance, "ostacolare il passaggio" is a somewhat awkward rendering of "contradiare il passamento," which could have been expressed more naturally. Additionally, the term "camerlingo" is correctly preserved, but the phrase "presenza di messer il papa" feels slightly mechanical compared to the original "presenzia di messer lo papa." While the translation is comprehensible and conveys the main idea, it lacks the elegance and fluency of a truly polished translation. The syntax is modern but occasionally rigid, indicating a translation that is generally good but not outstanding.</t>
         </is>
       </c>
+      <c r="K31" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.7319</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5563</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1905,6 +2301,18 @@
           <t>The translation captures the essence of the original text and maintains a modern Italian language structure while preserving the archaic elements. However, it shows some mechanical traits in the rendering of "fortemente meravigliandose," which could have been expressed more naturally as "con grande stupore." Additionally, the use of quotation marks around the dialogue ("") instead of the traditional Italian style ('') indicates a slight inconsistency with the conventions of Italian punctuation. While the translation is comprehensible and conveys the main message, it lacks the nuanced expression of the original's emotional depth and could benefit from a more refined choice of words. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K32" t="n">
+        <v>0.8836000000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.6331</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1949,6 +2357,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "affinché" instead of "acciocché" shows a good adaptation to contemporary language, though it could have been more elegant. The phrase "buon animo" is a suitable modern equivalent for "d'animo buono," but the construction "di mandare" feels slightly mechanical compared to the original's "di mandare." While the translation is comprehensible and conveys the intended message, it lacks the poetic nuance of the original, particularly in the final part where "per tranquillizzare la mia mente" would have been a better choice than "per avere buon animo." So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K33" t="n">
+        <v>0.8056</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.6976</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.7597</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1999,6 +2419,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax, though it could have been more elegant in rendering "porco salvatico". The term "cinghiale selvatico" is a good choice, but it slightly deviates from the original meaning. The phrase "supera l’uomo nell’udito e il lupo nel vedere" is comprehensible but lacks the poetic flair of the original. While the translation is functional and conveys the main idea, it misses some of the archaic charm and nuance present in the source text. The use of "dubbio" instead of "fallo" is a reasonable but not optimal choice, showing a slight tendency towards modernization. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K34" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.5800999999999999</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2043,6 +2475,18 @@
           <t>The translation captures the basic meaning of the original text but shows some mechanical traits. The phrase "in un punto" is a literal translation of "uno luogo," which sounds slightly awkward in modern Italian. The use of quotation marks around "capo di porco" instead of italics indicates a lack of understanding of how to handle archaic terms in modern translations. While the overall message is preserved, the translation lacks the natural flow and idiomaticity that would make it more engaging. The syntax follows the original too closely, resulting in a somewhat rigid construction. The translation is comprehensible but could benefit from more refined language choices and better adaptation to modern Italian conventions.</t>
         </is>
       </c>
+      <c r="K35" t="n">
+        <v>0.8072</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2089,6 +2533,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The archaic terms "cerbi" and "cinghiaire" are appropriately replaced with their modern equivalents "cerbiatti" and "cinghiale," showing good adaptation of terminology. However, the phrase "conosce bene" could have been more elegantly expressed as "sapeva bene" to better reflect the original's tone. The translation is generally fluent and comprehensible, though it occasionally leans towards a slightly mechanical rendering of the original, particularly in the final part where "dimora" is used instead of "dimori." While the translation is serviceable, it lacks the nuanced expression that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K36" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.5583</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2135,6 +2591,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "timorosi" instead of "disidrosi" shows a good attempt at adapting archaic terms to contemporary language, though it's not the most precise choice. The phrase "molte paure" for "varie e diverse paure" is a slight simplification but remains comprehensible. The second part of the sentence is handled well, with "cadrà a terra infilzato" being a clear and understandable rendering of the original. However, the translation lacks some of the poetic nuance present in the gold translation, particularly in the description of the wild boar. While the translation is functional and readable, it doesn't fully capture the rich imagery of the original text.</t>
         </is>
       </c>
+      <c r="K37" t="n">
+        <v>0.8873</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5770999999999999</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2185,6 +2653,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "incorporee" instead of "incorporate" shows a good attempt at preserving the archaic tone, though it could have been more precise. The phrase "non si trovano entro i corpi" is a literal translation that, while understandable, lacks the elegance of the original. The translation successfully conveys the main ideas but occasionally opts for a more straightforward rendering rather than capturing the full nuance of the medieval language. While the translation is generally accurate and comprehensible, it misses some of the stylistic sophistication of the original text.</t>
         </is>
       </c>
+      <c r="K38" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.8746</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.7953</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2229,6 +2709,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "through which" instead of "for which" represents a slight deviation from the original meaning, but it's a reasonable choice considering the context. The phrase "si amministrano e si giudicano" is a good adaptation of "dispensano e giudicano," though it could have been more elegant. The translation is comprehensible and conveys the intended message, but it lacks the poetic nuance of the original. While it's a solid translation, it doesn't fully capture the archaic tone of the source text, making it feel somewhat mechanical in places. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K39" t="n">
+        <v>0.9149</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2275,6 +2767,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "superava" instead of "passava" is a good adaptation, though it could have been more elegant. The phrase "a loro assegnato" is a reasonable choice for "deputato," but it's not the most idiomatic expression. The translation successfully conveys the main ideas about poets discussing their virtues and faults, but the phrasing occasionally feels slightly mechanical, particularly in the second sentence where the structure closely follows the original. While the translation is comprehensible and mostly accurate, it lacks the natural flow and sophistication that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K40" t="n">
+        <v>0.8362000000000001</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.7338</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2319,6 +2823,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "retta" instead of "diritta" shows a good understanding of archaic-to-modern Italian vocabulary transformation. However, the phrase "quella sola penso essere il bene" feels slightly mechanical and could have been expressed more naturally as "penso che quella cosa sia il bene." The translation is comprehensible and conveys the main message, but it lacks the elegance and flow that would make it truly outstanding. The handling of the archaic terms is adequate, though not perfect, and the overall structure follows the original too closely in places. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K41" t="n">
+        <v>0.8677</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.8933</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.8342000000000001</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2363,6 +2879,18 @@
           <t>The translation captures the essence of the original text and maintains its readability in modern Italian, though it shows some mechanical traits. The use of "avvelenavano" instead of "si scontravano" slightly deviates from the original meaning, as it implies a more active engagement with the venom than the original text suggests. The term "Psilli" is correctly preserved, but the phrase "nel loro stesso veleno" is a somewhat literal rendering of "inazzi della loro salive," which could have been expressed more naturally. While the translation is comprehensible and conveys the main idea, it lacks the nuanced expression of the original's cultural context and could benefit from more idiomatic language choices.</t>
         </is>
       </c>
+      <c r="K42" t="n">
+        <v>0.8538</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2405,6 +2933,18 @@
           <t>The translation captures the essence of the original text but exhibits some mechanical qualities. While it maintains the core meaning, the phrase "dietro o nel sedere" feels slightly awkward and could have been expressed more naturally as "dall'altro lato." The use of "coi propri occhi" instead of "con gli occhi" shows a tendency towards literal translation rather than idiomatic expression. The text remains comprehensible and conveys the intended message, though it lacks the smoothness and natural flow of a fully polished translation.</t>
         </is>
       </c>
+      <c r="K43" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.6569</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.5807</v>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2449,6 +2989,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "materiali" instead of "corporali" shows a slight deviation from the original meaning, though it remains comprehensible. The phrase "anche questa fu colpa tua" is a good adaptation of the archaic expression, but the construction "perché volevi" could have been more elegantly expressed. While the translation is generally accurate and readable, it lacks the nuanced elegance of a higher-scoring translation, particularly in the handling of the archaic elements. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K44" t="n">
+        <v>0.8816000000000001</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.9233</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2499,6 +3051,18 @@
           <t>The translation captures the essence of the original text and maintains its basic meaning, but there are noticeable issues with the archaic language elements. The phrase "non tine rispondo" is simplified to "non rispondo," losing some of the medieval flavor. Additionally, the word "ttu" is replaced with the more modern "tu," which doesn't fully preserve the archaic tone. While the translation is comprehensible and conveys the main ideas, it lacks the stylistic richness of the original text. The use of "momento" instead of "tempo" also slightly diminishes the historical authenticity. The translation is functional but could benefit from more careful attention to the linguistic nuances of the original.</t>
         </is>
       </c>
+      <c r="K45" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.8631</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2543,6 +3107,18 @@
           <t>The translation captures the essence of the original text and conveys the main idea accurately, but there are noticeable mechanical elements in the phrasing. The use of "è giusto" instead of "sì convene" slightly alters the archaic tone, while "una grande somma" is a somewhat literal translation of "grande avere." The sentence structure follows modern Italian conventions, making it accessible, but the choice of "se ne andasse" feels slightly forced compared to the original's "lasciasse andare via." While the translation is comprehensible and functional, it lacks the nuanced expression of the medieval language style.</t>
         </is>
       </c>
+      <c r="K46" t="n">
+        <v>0.7641</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.7635</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2587,6 +3163,18 @@
           <t>The translation captures the main message of the original text but shows some mechanical traits in its construction. The use of "coloro che" instead of "chiunque" slightly deviates from the original's style, while "tradimento" is a more modern term than "tradigione." The syntax follows a somewhat rigid pattern, particularly in the second sentence, which could have been expressed more naturally. While the translation conveys the essential meaning, it lacks the nuanced expression of the original's archaic tone, and the word choices are occasionally too contemporary for the context. The translation is comprehensible and functional, but it doesn't fully capture the stylistic elements of the medieval text.</t>
         </is>
       </c>
+      <c r="K47" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.7752</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.7532</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2635,6 +3223,18 @@
           <t>The translation captures the essence of the original text and conveys the main ideas accurately, but there are noticeable mechanical elements in the phrasing. The use of "tanto che" instead of "così che" slightly alters the original tone, and the omission of "egualmente" at the end makes the comparison less explicit than the source text. While the translation remains comprehensible and modern, it doesn't fully capture the archaic style of the original, which could have been better preserved through more careful word choice. The syntax is generally correct but lacks the nuanced expression found in high-quality translations. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K48" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.7435</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.6111</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2683,6 +3283,18 @@
           <t>The translation captures the essence of the original text and conveys the main ideas accurately, but there are noticeable mechanical elements in the phrasing. For instance, "dandogli il regno" could have been expressed more naturally as "dando il regno a lui." Additionally, the use of "capitò di governare" feels somewhat literal and lacks the elegance of the original. While the translation is comprehensible and maintains the basic meaning, it doesn't fully capture the stylistic nuances of the medieval Italian text. The modernization of archaic terms is adequate but not optimal, and the syntax occasionally feels slightly forced. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K49" t="n">
+        <v>0.8072</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.7667</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2733,6 +3345,18 @@
           <t>The translation captures the main idea of the original text but shows some mechanical traits in its construction. While it successfully conveys the concept of the soul's transformation based on the body's characteristics, it uses "caratteristiche" instead of the more appropriate "proprietà," which slightly deviates from the original meaning. The syntax is modern and comprehensible, though it lacks the poetic nuance of the original. The translation is readable and understandable, but it doesn't fully capture the archaic tone of the source text, making it feel somewhat mechanical rather than naturally flowing. The use of "si unisce" is adequate but could have been more elegantly expressed to better match the original's style.</t>
         </is>
       </c>
+      <c r="K50" t="n">
+        <v>0.9489</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.9251</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.8744</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2777,6 +3401,18 @@
           <t>The translation captures the essence of the original text and maintains its meaning, though it shows some mechanical aspects in the rendering of certain phrases. For instance, "non uniti nella carne" could have been expressed more naturally as "non più due". The use of "bensì" instead of "ma" slightly alters the flow of the original text. While the translation is comprehensible and conveys the main ideas, it lacks the stylistic finesse and idiomaticity that would elevate it to a higher score. The adaptation of archaic terms into modern Italian is adequate but not optimal, particularly in the final sentence where the phrase "con lui" feels somewhat forced. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K51" t="n">
+        <v>0.8635</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.8273</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.7207</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2821,6 +3457,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "ve lo raccontiamo" instead of "il vi raccontiamo" shows a good adaptation to contemporary language patterns. However, the phrase "la luce del lusso" could have been more elegantly expressed as "l'illuminazione del lusso," which would have better preserved the original's poetic tone. Additionally, the rendering of "sì cognobe" as "riconobbe per la prima volta" is somewhat literal and lacks the nuance of the original's "prima in grande." While the translation is generally accurate and comprehensible, it occasionally misses opportunities for more sophisticated expression.</t>
         </is>
       </c>
+      <c r="K52" t="n">
+        <v>0.8362000000000001</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.7112000000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.4799</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2865,6 +3513,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "è doloroso da sentire" effectively conveys the emotional weight of the original phrase. However, the translation of "con grandissimo disonore" feels slightly mechanical and could have been expressed more naturally. The addition of "gli uomini" in parentheses shows an attempt to clarify the archaic reference, though it's not necessary for the modern reader. While the translation is generally accurate and comprehensible, it lacks the nuanced expression of the original's poetic style. The modernization of the text is adequate but not fully polished, indicating a good but not outstanding translation.</t>
         </is>
       </c>
+      <c r="K53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.7766</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2909,6 +3569,18 @@
           <t>The translation captures the basic meaning of the original text but exhibits some mechanical qualities. While it conveys the idea that Christ was not bothered by the words, the phrasing "non provò fastidio ad ascoltare" feels slightly awkward and could be more idiomatic. The use of "tali parole" instead of "quelle parole" shows a tendency towards literal translation rather than natural expression. The syntax follows the original too closely, making it read somewhat like a machine translation. However, the translation remains comprehensible and maintains the core message, though it lacks the elegance and nuance of a fully human-rendered text.</t>
         </is>
       </c>
+      <c r="K54" t="n">
+        <v>0.7708</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.5944</v>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2953,6 +3625,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "costoro" instead of "loro" reflects a more formal tone, which aligns with the archaic nature of the source text. However, the phrase "l’atteggiamento" could have been better expressed as "lo studio" to maintain consistency with the original context. The translation successfully conveys the sense of observation and struggle against the multitude, though it slightly simplifies the original's complexity. While the overall meaning is preserved, the slight loss of nuance in certain phrases indicates room for improvement.</t>
         </is>
       </c>
+      <c r="K55" t="n">
+        <v>0.7893</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.5497</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2997,6 +3681,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The phrase "udire di belle novelle" is appropriately rendered as "ascoltare belle storie," preserving the meaning while using contemporary language. However, the use of "annusare" instead of "sentire il profumo" shows a slight preference for literal translation over idiomatic expression. The addition of "nel modo, nel tempo e nella misura" is a good attempt at capturing the original's emphasis on appropriateness, though it could have been more elegantly integrated into the sentence structure. While the translation is generally accurate and comprehensible, it occasionally leans towards a somewhat mechanical rendering of the original, particularly in the final part where the construction feels slightly forced.</t>
         </is>
       </c>
+      <c r="K56" t="n">
+        <v>0.8015</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.6999</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3041,6 +3737,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The phrase "come se stesse riflettendo" effectively conveys the original's "quasi come s'egli andasse pensando," though it could have been more elegant. The term "alloggio" is a suitable modern equivalent for "albergo," showing good adaptation of archaic terms. However, the translation lacks some of the poetic nuance present in the original, particularly in the rendering of "pensando alla risposta." While comprehensible and functional, the translation doesn't fully capture the subtle implications of the original text, making it read slightly mechanically at times.</t>
         </is>
       </c>
+      <c r="K57" t="n">
+        <v>0.8731</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.9061</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.8446</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3085,6 +3793,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "desideroso" instead of "disioso" shows a good attempt at modernizing the archaic term, though it could have been more precise. The phrase "recarmi là dove non posso andare con il corpo" is a bit mechanical compared to the original's poetic expression, indicating a slight loss of the original's stylistic richness. While the translation is comprehensible and conveys the main message, it lacks the nuanced elegance of a truly excellent translation. The sentence structure follows the original too closely, which makes it feel somewhat literal rather than naturally flowing in modern Italian.</t>
         </is>
       </c>
+      <c r="K58" t="n">
+        <v>0.8787</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.8915</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.7965</v>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3129,6 +3849,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "subito" instead of "di subito" shows a slight preference for contemporary language, though it's not entirely necessary. The term "moltitudine" could have been replaced with a more idiomatic expression like "folla" to better match the original's style. While the translation is comprehensible and conveys the main idea, it lacks the poetic nuance present in the original text, particularly in the description of the birds' movement. The sentence structure is clear but somewhat rigid, indicating a moderate level of adaptation rather than a fully naturalized version. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K59" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.9392</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.8772</v>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3173,6 +3905,18 @@
           <t>The translation captures the main idea of the original text but shows some mechanical traits in its construction. While it maintains the core meaning, the phrase "sa dare un giudizio vero" feels slightly awkward and could have been expressed more naturally. The use of "su ogni cosa" instead of "di tutte le cose" represents a slight deviation from the original, though it remains comprehensible. The translation demonstrates a good grasp of the source material but lacks the finesse and elegance that would elevate it to a higher score. The modernization of archaic terms is adequate but not optimal, showing room for improvement in terms of idiomatic expression.</t>
         </is>
       </c>
+      <c r="K60" t="n">
+        <v>0.8464</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.8607</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3217,6 +3961,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The phrase "Ecco fino a che punto" effectively conveys the meaning of "Or ecco quanto," though it slightly deviates from the original's conciseness. The use of "a causa della sua superbia" instead of a more direct translation shows an attempt to adapt the text to contemporary language, but it introduces a slight redundancy. While the translation is comprehensible and maintains the core message, it could have been more elegant in its construction, particularly in the final part where "in alto" is repeated unnecessarily. The translation demonstrates a good understanding of the source material but lacks the refinement expected of a higher score.</t>
         </is>
       </c>
+      <c r="K61" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.8609</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.7455000000000001</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3263,6 +4019,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "caratteristica" instead of "proprietà" shows a slight preference for a more contemporary term, which is acceptable but not ideal. The phrase "nella aria" is a good adaptation of "per l'aire," though it could have been more elegant. The translation is comprehensible and conveys the main idea, but it lacks the poetic nuance of the original, particularly in the rendering of "sì come." While the translation is serviceable, it doesn't fully capture the archaic charm of the source text. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K62" t="n">
+        <v>0.8908</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.8486</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3307,6 +4075,18 @@
           <t>The translation maintains the basic meaning of the original text but shows some mechanical traits in its construction. The use of commas instead of proper punctuation marks ("si scrivono,") makes it appear slightly awkward. While the translation is comprehensible, it lacks the natural flow of a high-quality translation. The phrase "si giura" is a literal rendering of "giurano," which could have been expressed more idiomatically. The text is readable but doesn't fully capture the stylistic nuances of the original medieval Italian. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K63" t="n">
+        <v>0.9384</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.9113</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.8627</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3351,6 +4131,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "ribadisco" instead of "ripeto" adds a slight nuance of authority, which is appropriate for the context. However, the phrase "secondo il tuo insegnamento" could have been more elegantly expressed as "secondo il tuo comandamento," which would have better preserved the archaic tone. The translation is generally fluent and comprehensible, though it occasionally leans towards a slightly mechanical rendering of the original. While it successfully conveys the main message, it lacks some of the stylistic finesse that would elevate it to a higher score. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K64" t="n">
+        <v>0.8769</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.7999000000000001</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.6758</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3399,6 +4191,18 @@
           <t>The translation captures the essence of the original text and conveys the main ideas accurately, but there are noticeable issues with the phrasing and word choices. The use of "degne di memoria" instead of "per fare" loses some of the original's poetic quality. Additionally, the sentence structure follows the original too closely, resulting in somewhat rigid constructions. While comprehensible, the translation lacks the natural flow of a high-quality human translation, particularly in the second sentence where the syntax feels forced. The archaic elements are preserved, but the modernization could be more elegant. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K65" t="n">
+        <v>0.8299</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.8147</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.5542</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3443,6 +4247,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "insuperbisca" instead of "inorgoglisca" shows a slight preference for archaic terms, which could have been better adapted to the modern context. The phrase "vedendo le sue lodi" is a good adaptation of the original "vedendo le sue laudi," though it could have been more elegant. While the translation is generally accurate and comprehensible, it occasionally leans towards a more literal rendering rather than a fully naturalized expression. The text flows well but lacks the refinement expected of a higher score.</t>
         </is>
       </c>
+      <c r="K66" t="n">
+        <v>0.8682</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.7644</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3487,6 +4303,18 @@
           <t>The translation captures the main idea of the original text but shows some mechanical traits. While it correctly conveys the basic information about Saint Augustine's book, the phrase "scrisse un libro che si chiamava" is a somewhat literal rendering of the original construction, which could have been expressed more naturally in modern Italian. The use of "La Città di Dio" instead of "Agostino della Città di Dio" represents a slight loss of the original's emphasis on the author's name. The translation is comprehensible and maintains the overall meaning, but lacks the stylistic refinement expected of a higher-quality translation.</t>
         </is>
       </c>
+      <c r="K67" t="n">
+        <v>0.8963</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.9371</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.7713</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3531,6 +4359,18 @@
           <t>The translation captures the essence of the original text and maintains its meaning, though it could have been more elegant. The phrase "non si può limitare a una regola" is a good modern equivalent for "non si può stringere a legge," but it's slightly mechanical compared to the gold translation. The use of "non ho mai sentito dire" instead of "non udii mai che egli avesse" is a reasonable choice, though it loses some of the archaic flavor. While the translation is comprehensible and conveys the message, it doesn't fully capture the poetic nature of the original text. The syntax is modern and clear, but there's room for improvement in terms of style and nuance. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K68" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.9301</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3581,6 +4421,18 @@
           <t>The translation demonstrates exceptional fluency and precision while maintaining the archaic essence of the original text. The modern Italian rendering is both natural and respectful of the source content, successfully conveying the medieval context without compromising readability. The syntax flows smoothly, and the archaic term "oltramare" is appropriately preserved, reflecting the original's historical authenticity. The translation achieves a perfect balance between modern accessibility and historical accuracy, making it indistinguishable from a translation crafted by a highly skilled human translator.</t>
         </is>
       </c>
+      <c r="K69" t="n">
+        <v>0.7768</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.7058</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.7239</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3625,6 +4477,18 @@
           <t>This translation is severely flawed and fails to convey the original message. The text is nonsensical and lacks coherence, with phrases like "cosa che è ancora più grave" and "fuggire, e lasciare che il proprio Comune" that make no sense in context. The archaic terms have been completely mishandled, with "cavaliere" being replaced with an unrelated concept about capture and escape. The syntax is broken and the meaning is unclear, making it impossible to understand what the original text was trying to communicate. The translation demonstrates a clear lack of understanding of both the source language and the intended meaning, rendering it unusable for any purpose.</t>
         </is>
       </c>
+      <c r="K70" t="n">
+        <v>0.6257</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3669,6 +4533,18 @@
           <t>This translation is completely inadequate and fails to convey the meaning of the original text. The archaic terms "suo Comune" are left untranslated, making the text nearly incomprehensible to modern readers. The syntax is awkward and follows the original's structure too closely, resulting in a text that doesn't flow naturally in modern Italian. The phrase "e, cosa che anche è più grave" is a word-for-word translation that makes no sense in modern Italian, showing a lack of understanding of both languages' conventions. The use of "o vero" instead of "oppure" or "o" demonstrates a poor grasp of Italian conjunctions. The translation lacks any attempt to adapt the text to contemporary language norms, rendering it unusable for communication purposes.</t>
         </is>
       </c>
+      <c r="K71" t="n">
+        <v>0.8201000000000001</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.7489</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3713,6 +4589,18 @@
           <t>The translation captures the essence of the original text and maintains its meaning, though it could have been more elegant in certain phrases. The use of "dovete sapere" instead of "sappiate" slightly alters the formal tone, making it less archaic than the source text. While the translation is comprehensible and conveys the message effectively, it lacks the nuanced expression of the original's historical context. The phrase "così affrettati" is a somewhat literal rendering of "sì affrettati," which could have been expressed more naturally in modern Italian. The syntax is correct and the text flows well, but it doesn't fully capture the stylistic elements of the medieval language. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K72" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.9578</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.8411</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3753,6 +4641,18 @@
           <t>The translation captures the essence of the original text and maintains its meaning, though it could have been more elegant in certain phrases. The use of "popolo acheo" instead of "gente achea" shows a slight preference for modern terminology over archaic terms, which is acceptable but not ideal. The sentence structure is clear and comprehensible, but there's room for improvement in the flow and naturalness of the language. The translation successfully conveys the sense of shame and the decision-making process, though it doesn't fully capture the poetic quality of the original. While it's a good translation, it lacks the refinement and sophistication that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K73" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.6551</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.5817</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3803,6 +4703,18 @@
           <t>The translation captures the essence of the original text and maintains its meaning, though it could have been more elegant in certain phrases. The use of "intento" instead of "acconciamento" is a good choice, but "dimore" for "magioni" is slightly less common than "case". The syntax is modern and comprehensible, but there's room for improvement in the flow of the sentence. While the translation is accurate, it doesn't fully capture the poetic nature of the original text, which could have been better preserved. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K74" t="n">
+        <v>0.8925</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.7466</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3847,6 +4759,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "chi" instead of "colui" reflects a contemporary approach, though it slightly alters the archaic tone. The phrase "come se stesso" is a good adaptation of "come sé medesimo," preserving the meaning while using more accessible language. However, the translation could have been more elegant in rendering "giudicii" as "giudizi," which would have better preserved the original's formal tone. The sentence structure is clear and comprehensible, but the slight shift in formality makes it less than perfect. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K75" t="n">
+        <v>0.8854</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.9243</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8076</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3893,6 +4817,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "spiegato" instead of "impantanato" shows a slight departure from the archaic style, though it remains comprehensible. The phrase "in salvo" is a good adaptation of "salvamente," but the choice of "cinghiale" over "porco" loses some of the original's rustic charm. While the translation is functional and conveys the message, it lacks the full richness of the medieval language and could benefit from more nuanced word choices to better reflect the original's tone.</t>
         </is>
       </c>
+      <c r="K76" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3937,6 +4873,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian language structure. The use of "li aprii" instead of "gli apersi" shows a slight deviation from the archaic form, but it's still comprehensible. The phrase "che bisogno c'è" is a good adaptation of the original "che bisogno è," though it could have been more elegant. The translation successfully conveys the emotional tone of the original, particularly in the final part about the heart being closed to Christ. However, the choice of "sposo Cristo" instead of "sposo di Cristo" slightly diminishes the religious context. While the translation is generally good, it lacks the refinement and nuance that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K77" t="n">
+        <v>0.8913</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.8675</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.6158</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3981,6 +4929,18 @@
           <t>The translation maintains the basic meaning of the original text but exhibits several mechanical traits. The phrase "non puoi vivere bene qui" is a literal translation of "non puoi buonamente qui dimorare," which sounds awkward in modern Italian. Additionally, the use of "dubiti di andartene" instead of "hai pensato di andartene" shows a lack of idiomatic expression. The syntax follows the original too closely, resulting in a somewhat rigid construction that doesn't capture the natural flow of modern Italian. While the translation is comprehensible, it lacks the stylistic refinement and cultural adaptation expected in a higher-quality translation.</t>
         </is>
       </c>
+      <c r="K78" t="n">
+        <v>0.8572</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.7917999999999999</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.7049</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4021,6 +4981,18 @@
           <t>The translation captures the main meaning of the original text but shows some mechanical traits in its construction. The use of "volendo restare" instead of "volendo dimorare" represents a slight deviation from the original archaic style, though it remains comprehensible. The phrase "che era incitata" is a somewhat literal rendering of the original, which could have been expressed more naturally as "che incitarono." While the translation is generally accurate and readable, it lacks the nuanced expression of the original's historical context and could benefit from a more sophisticated handling of the archaic elements. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K79" t="n">
+        <v>0.9082</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.8396</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.7237</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4065,6 +5037,18 @@
           <t>The translation demonstrates exceptional fluency while maintaining the archaic essence of the original text. The phrase "a cui viene affidata" perfectly captures the medieval tone while being accessible to modern readers. The use of "sorte" instead of "ventura" shows careful consideration of contemporary language preferences while preserving the original meaning. The syntax flows naturally, and there's no trace of machine-generated text, making it indistinguishable from a human translation. The translation successfully balances modern readability with historical accuracy, rendering the archaic terms with precision and respect for the source content.</t>
         </is>
       </c>
+      <c r="K80" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.8641</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4109,6 +5093,18 @@
           <t>The translation captures the essence of the original text and maintains its basic meaning, but there are noticeable issues with the rendering of certain archaic terms. For instance, "MMMD" was incorrectly converted to "3500," which is a significant error in historical context. The phrase "sorte diversa" is a somewhat literal translation of "diversa ventura," missing the nuance of fortune or luck. While the overall structure is comprehensible, the translation occasionally falls into a mechanical pattern, particularly in the handling of the historical references. The text remains readable but lacks the sophistication and elegance expected from a high-quality translation.</t>
         </is>
       </c>
+      <c r="K81" t="n">
+        <v>0.8838</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.8101</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.7466</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4153,6 +5149,18 @@
           <t>The translation captures the basic meaning of the original text but shows some mechanical traits in its construction. The use of "ricompensati" instead of "iscaciati" represents a significant departure from the source text's meaning, which could lead to confusion about the intended message. While the syntax is modern and comprehensible, the choice of "merito" and "buona sorte" feels somewhat literal and lacks the nuance of the original "ventura buona." The translation maintains readability but misses the opportunity to employ more idiomatic expressions that would make it feel more natural in modern Italian. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K82" t="n">
+        <v>0.8327</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.5774</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4193,6 +5201,18 @@
           <t>The translation maintains the basic meaning of the original text but shows some mechanical qualities. While it successfully conveys the core message about divine prayers and victory, the phrasing "le vostre preghiere sono efficaci" feels slightly literal and could have been expressed more naturally. The use of "ebbe fortuna" instead of "ha avuto fortuna" is a good adaptation, though it's not the most elegant choice. The syntax follows the original too closely in places, making it read somewhat like a machine translation. The translation is comprehensible and functional, but lacks the refinement and idiomaticity that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K83" t="n">
+        <v>0.8958</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.8638</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.8401</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4241,6 +5261,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "sceriffi" instead of "principi" shows an attempt to modernize the language, though it could have been more precise. The phrase "si sistemò nella casa" is a good adaptation of "allogò ne la casa," but the expression "poiché era così che" feels slightly mechanical compared to the original "con ciò fosse cosa che." While the translation is comprehensible and conveys the main ideas, it lacks the nuanced historical flavor present in the gold translation. The choice of "correvano" for "scherani" is adequate but not optimal, as it doesn't fully capture the medieval context. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K84" t="n">
+        <v>0.8683999999999999</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.6608000000000001</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.5007</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4291,6 +5323,18 @@
           <t>The translation captures the essence of the original text and maintains its formal tone, though it occasionally uses slightly mechanical constructions such as "contro di lui" instead of the more idiomatic "contro lui". The term "discendenza" for "ingenerazione" is a reasonable but not optimal choice, as "stirpe" would have been more authentic to the medieval context. While the translation is comprehensible and conveys the main ideas, it lacks some of the stylistic finesse expected in high-quality translations. The syntax follows modern Italian conventions but doesn't fully capture the archaic flavor of the original. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K85" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.9002</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.8028</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4335,6 +5379,18 @@
           <t>The translation captures the basic meaning of the original text but exhibits some mechanical qualities. The phrase "fu spinta" is a literal rendering of "si fue impinto," which could have been expressed more naturally as "si fece navigare." Additionally, "passaggio pericoloso" is a somewhat awkward translation of "trapasso periglioso," where "strato" would have been more appropriate. While the translation is comprehensible, it lacks the elegance and idiomaticity expected in high-quality Italian. The use of "piovosa" instead of "pioggia" shows a slight over-reliance on modern vocabulary, though it's not incorrect. The text maintains the essential meaning but misses opportunities for more refined expression.</t>
         </is>
       </c>
+      <c r="K86" t="n">
+        <v>0.7945</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.7769</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4379,6 +5435,18 @@
           <t>The translation captures the essence of the original text and maintains its basic meaning, but there are noticeable issues with the flow and expression. The phrase "nel caso si potessero difendere" is a somewhat mechanical rendering of the original's "se da alto si potessero difendere," which loses the nuance of the conditional aspect. Additionally, the use of "scappare" instead of "scampare" slightly alters the connotation of the original text, making it less aligned with the medieval context. While the translation is comprehensible and conveys the main idea, it lacks the stylistic refinement expected of a higher-quality translation. The modernization of the text is adequate but could benefit from more idiomatic expressions to better reflect the original's tone.</t>
         </is>
       </c>
+      <c r="K87" t="n">
+        <v>0.8015</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.8303</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4425,6 +5493,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "elevato" instead of "alto" and "visione sottile" for "sottil vista" shows a good understanding of the archaic terms. However, the phrase "superata la vastità dell’università (o della totalità)" introduces unnecessary ambiguity and could have been expressed more elegantly. The translation is comprehensible and conveys the main ideas, but it lacks the poetic nuance of the original, particularly in the final part where "forma semplice" is used instead of "sguardo." While the translation is serviceable, it doesn't fully capture the stylistic richness of the medieval text.</t>
         </is>
       </c>
+      <c r="K88" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.7896</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.7062</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4475,6 +5555,18 @@
           <t>The translation maintains the basic structure and meaning of the original text, preserving the metaphorical comparison between the eye and the salutation. However, it shows some mechanical traits in the rendering of "pistola" as "lettera," which could have been better adapted to "saluto" or "salutazione." The syntax follows the original too closely, resulting in a slightly awkward construction. While comprehensible, the translation lacks the natural flow and idiomaticity that would make it more engaging. The use of "allora" instead of "dunque" slightly diminishes the archaic tone of the original. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K89" t="n">
+        <v>0.8801</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.7342</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4519,6 +5611,18 @@
           <t>The translation captures the main idea of the original text but shows some mechanical traits in its construction. The use of "che" instead of "i quali" slightly reduces the formal tone of the original, while "formavano" is a somewhat literal rendering of "facta." The phrase "di Greci" is awkwardly constructed and doesn't fully capture the original's nuance about Greek nobility. While the translation is comprehensible and conveys the basic meaning, it lacks the elegance and sophistication of a high-quality translation. The text reads as if it were produced by a competent human translator rather than a machine, but there's room for improvement in terms of idiomaticity and naturalness.</t>
         </is>
       </c>
+      <c r="K90" t="n">
+        <v>0.8744</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.8449</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.7753</v>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4563,6 +5667,18 @@
           <t>The translation captures the essence of the original text and maintains its basic meaning, but there are noticeable issues with the flow and readability. The use of "era" instead of "fu" creates a slight temporal ambiguity, and the sentence structure feels somewhat mechanical. While the translation is comprehensible, it lacks the naturalness and elegance of a high-quality translation. The archaic terms are handled adequately, but the overall construction doesn't fully capture the stylistic nuances of the medieval text. The translation would benefit from more refined language choices and better integration of the archaic elements into modern Italian.</t>
         </is>
       </c>
+      <c r="K91" t="n">
+        <v>0.8727</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.9061</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.8463000000000001</v>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4611,6 +5727,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "Poiché" instead of "però" shows an attempt to modernize the language, though it could have been more elegant. The term "misericordia" is a good choice for "pietà," but the phrase "saper avere" feels slightly mechanical compared to the original "sapere avere." While the translation is comprehensible and conveys the main message, it lacks the poetic nuance of the original, particularly in the final part where "nonn è meno laudabile" is rendered too literally as "non è meno lodabile." The translation demonstrates a good understanding of the source text but misses opportunities for more natural expression.</t>
         </is>
       </c>
+      <c r="K92" t="n">
+        <v>0.8729</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.8754999999999999</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4655,6 +5783,18 @@
           <t>The translation captures the essence of the original text and maintains its basic meaning, but there are noticeable issues with the archaic language adaptation. The term "genero" is used instead of the more appropriate "suocero," which shows a slight lack of precision in conveying the relationship. Additionally, the phrase "di Phausonia" could have been better rendered as "da Faustonia" to maintain consistency with the original text's style. While the translation is comprehensible and conveys the main message, it lacks the nuanced expression of the original's formal tone. The syntax is modern but sometimes feels slightly mechanical, particularly in the construction of the final sentence. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K93" t="n">
+        <v>0.8761</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.6536999999999999</v>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4699,6 +5839,18 @@
           <t>The translation captures the basic meaning of the original text but exhibits some mechanical qualities. While it conveys the idea of someone being wealthy and unhappy with their spouse, the phrasing "diversa da quella che ha" feels slightly awkward compared to the more idiomatic "al posto di quella che ha." The use of "si lamenta" instead of "lamentasi" represents a modernization that is appropriate but could have been expressed more elegantly. The translation maintains the core message but lacks the nuanced expression of the original's archaic tone. The sentence structure follows the original closely, which results in a somewhat rigid construction that doesn't fully capture the natural flow of modern Italian.</t>
         </is>
       </c>
+      <c r="K94" t="n">
+        <v>0.8389</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.8589</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.7163</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4743,6 +5895,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "visione" instead of "figura" is a good adaptation of the archaic term, though it could have been more precise. The quotation marks around "Uccidi e mangia" are appropriate, but the sentence structure remains somewhat rigid, indicating a slight mechanical approach. While the translation is comprehensible and conveys the main message, it lacks the nuanced expression of the original medieval text, particularly in the rendering of "popolo Gentile." The choice of "popolo" over "popolazione" or "popolo pagano" shows a missed opportunity to capture the historical context fully. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K95" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.8289</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4783,6 +5947,18 @@
           <t>The translation captures the essence of the original text and maintains a modern Italian syntax while preserving the core meaning. However, it shows some mechanical traits in the rendering of archaic terms, such as "obbligazione" which could have been better expressed as "impegno" or "contratto". The phrase "ne fece un documento scritto" is a slight oversimplification of the original "fecene carta", losing some of the historical nuance. While the translation is comprehensible and functional, it lacks the stylistic refinement expected of a higher score. The text flows naturally but occasionally uses expressions that feel slightly mechanical rather than organic. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="K96" t="n">
+        <v>0.8401</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.7996</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.6741</v>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4827,6 +6003,18 @@
           <t>The translation maintains the archaic tone of the original text while making it accessible to modern readers. The use of "Che cosa rappresentiamo" instead of "Che figuriamo" shows a slight departure from the original, but this choice is reasonable given the modern context. The phrase "quel popolo" is a good adaptation of "il qual populo," though it could have been more elegant. The syntax is generally correct, but there's room for improvement in terms of flow and naturalness. The translation captures the essence of the original but occasionally leans towards a more literal rendering, particularly in the final sentence where "ha tenuto" could have been expressed more idiomatically. While the translation is comprehensible and conveys the main message, it lacks the refinement and sophistication that would elevate it to a higher score.</t>
         </is>
       </c>
+      <c r="K97" t="n">
+        <v>0.8878</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.7625999999999999</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.5369</v>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4871,6 +6059,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The use of "perché" instead of "ch'io non lo sofferrò e non lo lascerò" shows a slight shift towards a more contemporary expression, though it still retains the original's meaning. While the translation is generally accurate, it could have better preserved the archaic tone of the original text, particularly in the second part where "non lo sopporterò e non lo permetterò" feels somewhat literal and lacks the poetic nuance of the source. The text remains comprehensible and natural, but there's room for improvement in capturing the full emotional depth of the original.</t>
         </is>
       </c>
+      <c r="K98" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.8907</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.8461</v>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
